--- a/Tabela e Gráfico Speedup e Eficiência_Paralelizar avaliador de arquivos de log.xlsx
+++ b/Tabela e Gráfico Speedup e Eficiência_Paralelizar avaliador de arquivos de log.xlsx
@@ -148,11 +148,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="21353528"/>
-        <c:axId val="2057979616"/>
+        <c:axId val="496473391"/>
+        <c:axId val="1015645421"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21353528"/>
+        <c:axId val="496473391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -204,10 +204,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2057979616"/>
+        <c:crossAx val="1015645421"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2057979616"/>
+        <c:axId val="1015645421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -271,7 +271,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21353528"/>
+        <c:crossAx val="496473391"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -319,7 +319,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Planilha1!$B$3</c:f>
+              <c:f>Planilha1!$B$2</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -339,17 +339,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$B$4:$B$7</c:f>
+              <c:f>Planilha1!$B$3:$B$7</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1251136303"/>
-        <c:axId val="692377805"/>
+        <c:axId val="1493178120"/>
+        <c:axId val="898496361"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1251136303"/>
+        <c:axId val="1493178120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -401,10 +401,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692377805"/>
+        <c:crossAx val="898496361"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="692377805"/>
+        <c:axId val="898496361"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -468,7 +468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1251136303"/>
+        <c:crossAx val="1493178120"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -514,11 +514,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="720532292"/>
-        <c:axId val="281663709"/>
+        <c:axId val="126673126"/>
+        <c:axId val="772105433"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="720532292"/>
+        <c:axId val="126673126"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -570,10 +570,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="281663709"/>
+        <c:crossAx val="772105433"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="281663709"/>
+        <c:axId val="772105433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -648,7 +648,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="720532292"/>
+        <c:crossAx val="126673126"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
